--- a/data/excel/Autommerce_Partners_UAE.xlsx
+++ b/data/excel/Autommerce_Partners_UAE.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$145</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:D145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -508,17 +508,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Radiant</t>
+          <t>United SEO</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>https://byradiant.com</t>
+          <t>https://unitedseo.ae</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -530,39 +530,39 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Horizontal Digital</t>
+          <t>Push MENA</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>https://horizontaldigital.com</t>
+          <t>https://pushgroup.ae</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Huptech Web</t>
+          <t>True North Marketing</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://huptechweb.com</t>
+          <t>https://truenorthmarketing.ae</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -574,12 +574,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Webventis</t>
+          <t>Adapts Media</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://webventis.com</t>
+          <t>https://adaptsmedia.com</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Scarlet Media</t>
+          <t>Radiant</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>https://scarletmedia.net</t>
+          <t>https://byradiant.com</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -618,61 +618,61 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Think Tribe</t>
+          <t>Horizontal Digital</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>https://think-tribe.com</t>
+          <t>https://horizontaldigital.com</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Karve Digital</t>
+          <t>Huptech Web</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>https://karvedigital.com</t>
+          <t>https://huptechweb.com</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Centric</t>
+          <t>Webventis</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>https://centricdxb.com</t>
+          <t>https://webventis.com</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -684,17 +684,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Masterly</t>
+          <t>Scarlet Media</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>https://themasterly.com</t>
+          <t>https://scarletmedia.net</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -706,83 +706,83 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Imaga</t>
+          <t>Think Tribe</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>https://imaga.ai</t>
+          <t>https://think-tribe.com</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>AlCaz Media</t>
+          <t>Karve Digital</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>https://alcazmedia.ae</t>
+          <t>https://karvedigital.com</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Pluspoint Digital</t>
+          <t>Centric</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>https://pluspointdigital.com</t>
+          <t>https://centricdxb.com</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>RIS Services DMCC</t>
+          <t>Masterly</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>https://risservices.ae</t>
+          <t>https://themasterly.com</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Eureka Labs</t>
+          <t>Imaga</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>https://eurekalabs.io</t>
+          <t>https://imaga.ai</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -816,61 +816,61 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Omnisys Solutions</t>
+          <t>AlCaz Media</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>https://omnisyssolutions.com</t>
+          <t>https://alcazmedia.ae</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>EdgeFirm</t>
+          <t>Pluspoint Digital</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>https://edgefirm.io</t>
+          <t>https://pluspointdigital.com</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Wavai</t>
+          <t>RIS Services DMCC</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>https://wavai.ae</t>
+          <t>https://risservices.ae</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -882,17 +882,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Grafdom</t>
+          <t>Eureka Labs</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>https://grafdom.com</t>
+          <t>https://eurekalabs.io</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -904,61 +904,61 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ODN Digital</t>
+          <t>Omnisys Solutions</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>https://odndigital.com</t>
+          <t>https://omnisyssolutions.com</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Yaandu</t>
+          <t>EdgeFirm</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>https://yaandu.com</t>
+          <t>https://edgefirm.io</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Appinventiv</t>
+          <t>Wavai</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>https://appinventiv.com</t>
+          <t>https://wavai.ae</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Technology Consultants</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -970,61 +970,61 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>OSF Digital</t>
+          <t>Grafdom</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>https://osf.digital</t>
+          <t>https://grafdom.com</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Technology Consultants</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SEAL Infotech</t>
+          <t>ODN Digital</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>https://sealinfotech.ae</t>
+          <t>https://odndigital.com</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Synavos</t>
+          <t>Yaandu</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>https://synavos.com</t>
+          <t>https://yaandu.com</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1036,17 +1036,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>The Buzz People</t>
+          <t>Appinventiv</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>https://thebuzzpeople.com</t>
+          <t>https://appinventiv.com</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Fashion Ecommerce Technology Consultants</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1058,17 +1058,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Boomerang Middle East</t>
+          <t>OSF Digital</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>https://boomerang.ae</t>
+          <t>https://osf.digital</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Fashion Ecommerce Technology Consultants</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1080,39 +1080,39 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>To The Peak Studio</t>
+          <t>SEAL Infotech</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>https://tothepeak.studio</t>
+          <t>https://sealinfotech.ae</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Grassroots Agency</t>
+          <t>Synavos</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>https://gr.agency</t>
+          <t>https://synavos.com</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -1124,17 +1124,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Yallo</t>
+          <t>The Buzz People</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>https://yallo.co</t>
+          <t>https://thebuzzpeople.com</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Consulting Firms</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -1146,17 +1146,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Verticar</t>
+          <t>Boomerang Middle East</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>https://verticar.nl</t>
+          <t>https://boomerang.ae</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Technology Consultants</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -1168,17 +1168,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Renascence</t>
+          <t>To The Peak Studio</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>https://renascence.io</t>
+          <t>https://tothepeak.studio</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -1190,17 +1190,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Digital of Things</t>
+          <t>Grassroots Agency</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>https://digitalofthings.com</t>
+          <t>https://gr.agency</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Socio</t>
+          <t>Yallo</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>https://socio.ae</t>
+          <t>https://yallo.co</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
+          <t>Fashion Ecommerce Consulting Firms</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1234,17 +1234,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>upGrowth</t>
+          <t>Verticar</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>https://upgrowth.in</t>
+          <t>https://verticar.nl</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
+          <t>Fashion Ecommerce Technology Consultants</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -1256,17 +1256,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Right Media</t>
+          <t>Renascence</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>https://rightmedia.ae</t>
+          <t>https://renascence.io</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
+          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1278,17 +1278,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Notamedia</t>
+          <t>Digital of Things</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>https://notamedia.com</t>
+          <t>https://digitalofthings.com</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Sizing, Fit &amp; Returns Optimization Specialists</t>
+          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Newton Byte</t>
+          <t>Socio</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>https://newtonbyte.ae</t>
+          <t>https://socio.ae</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -1322,17 +1322,17 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Globify</t>
+          <t>upGrowth</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>https://globify.ae</t>
+          <t>https://upgrowth.in</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -1344,56 +1344,56 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Royex Technologies</t>
+          <t>Right Media</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>https://royex.ae</t>
+          <t>https://rightmedia.ae</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Tenet</t>
+          <t>Notamedia</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>https://wearetenet.com</t>
+          <t>https://notamedia.com</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
+          <t>Fashion Ecommerce Sizing, Fit &amp; Returns Optimization Specialists</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Experts in Shopify (MAQ Computer Services)</t>
+          <t>Newton Byte</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>https://expertsinshopify.com</t>
+          <t>https://newtonbyte.ae</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -1410,12 +1410,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>shopdev</t>
+          <t>Globify</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>https://shopdev.co</t>
+          <t>https://globify.ae</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>ZaUtre</t>
+          <t>Royex Technologies</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>https://zautre.com</t>
+          <t>https://royex.ae</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -1447,24 +1447,24 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>VIKST</t>
+          <t>Tenet</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>https://vikst.com</t>
+          <t>https://wearetenet.com</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -1476,17 +1476,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Ayata Commerce</t>
+          <t>Experts in Shopify (MAQ Computer Services)</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>https://ayatacommerce.com</t>
+          <t>https://expertsinshopify.com</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -1498,17 +1498,17 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Pixelique Digital</t>
+          <t>shopdev</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>https://pixeliquedigital.com</t>
+          <t>https://shopdev.co</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Feed Management Specialists</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -1520,17 +1520,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>e-Arabization</t>
+          <t>ZaUtre</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>https://e-arabization.com</t>
+          <t>https://zautre.com</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1542,34 +1542,34 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Codilar Technologies</t>
+          <t>VIKST</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>https://codilar.com</t>
+          <t>https://vikst.com</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Astound Digital (formerly Astound Commerce)</t>
+          <t>Ayata Commerce</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>https://astounddigital.com</t>
+          <t>https://ayatacommerce.com</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -1586,17 +1586,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Emakina MENA (now Empathy Lab by EPAM)</t>
+          <t>Pixelique Digital</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>https://empathylab.com</t>
+          <t>https://pixeliquedigital.com</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Product Feed Management Specialists</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -1608,17 +1608,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>scandiweb</t>
+          <t>e-Arabization</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>https://scandiweb.com</t>
+          <t>https://e-arabization.com</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -1630,12 +1630,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Creative971</t>
+          <t>Codilar Technologies</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>https://creative971.com</t>
+          <t>https://codilar.com</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1652,17 +1652,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>LUMINA Commerce</t>
+          <t>Astound Digital (formerly Astound Commerce)</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>https://luminacommerce.com</t>
+          <t>https://astounddigital.com</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -1674,17 +1674,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Prototype</t>
+          <t>Emakina MENA (now Empathy Lab by EPAM)</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>https://prototype.ae</t>
+          <t>https://empathylab.com</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1696,17 +1696,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GreenHonchos</t>
+          <t>scandiweb</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>https://greenhonchos.com</t>
+          <t>https://scandiweb.com</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Consulting &amp; Strategy Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -1718,12 +1718,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Shopvert</t>
+          <t>Creative971</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>https://shopvert.com</t>
+          <t>https://creative971.com</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -1733,19 +1733,19 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>The i.o agency</t>
+          <t>LUMINA Commerce</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>https://theioagency.com</t>
+          <t>https://luminacommerce.com</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -1762,83 +1762,83 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SQLI Middle East</t>
+          <t>Prototype</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>https://sqli.com</t>
+          <t>https://prototype.ae</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Vaimo</t>
+          <t>GreenHonchos</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>https://vaimo.com</t>
+          <t>https://greenhonchos.com</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Consulting &amp; Strategy Firms</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>20Three Digital</t>
+          <t>Shopvert</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>https://20three.digital</t>
+          <t>https://shopvert.com</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Microcorem</t>
+          <t>The i.o agency</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>https://microcorem.io</t>
+          <t>https://theioagency.com</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -1850,12 +1850,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Techies Infotech</t>
+          <t>SQLI Middle East</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>https://iamtechie.com</t>
+          <t>https://sqli.com</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -1865,19 +1865,19 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Krish TechnoLabs</t>
+          <t>Vaimo</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>https://krishtechnolabs.com</t>
+          <t>https://vaimo.com</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -1894,17 +1894,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Eastside Co</t>
+          <t>20Three Digital</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>https://eastsideco.com</t>
+          <t>https://20three.digital</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -1916,39 +1916,39 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Magneto IT Solutions</t>
+          <t>Microcorem</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>https://magnetoitsolutions.com</t>
+          <t>https://microcorem.io</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Valtech</t>
+          <t>Techies Infotech</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>https://valtech.com</t>
+          <t>https://iamtechie.com</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -1960,34 +1960,34 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>ArabyAds</t>
+          <t>Krish TechnoLabs</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>https://arabyads.com</t>
+          <t>https://krishtechnolabs.com</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Commerce9</t>
+          <t>Eastside Co</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>https://commerce9.io</t>
+          <t>https://eastsideco.com</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -1997,24 +1997,24 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>UN/COMMON</t>
+          <t>Magneto IT Solutions</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>https://uncommonagency.co</t>
+          <t>https://magnetoitsolutions.com</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2026,39 +2026,39 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Brainvire</t>
+          <t>Valtech</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>https://brainvire.com</t>
+          <t>https://valtech.com</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Gravityer</t>
+          <t>ArabyAds</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>https://gravityer.com</t>
+          <t>https://arabyads.com</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Kloc Technologies</t>
+          <t>Commerce9</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>https://kloctechnologies.com</t>
+          <t>https://commerce9.io</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -2092,61 +2092,61 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Chain Reaction</t>
+          <t>UN/COMMON</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>https://chainreaction.ae</t>
+          <t>https://uncommonagency.co</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Assembly MENA (Assembly Global)</t>
+          <t>Brainvire</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>https://assemblyglobal.com</t>
+          <t>https://brainvire.com</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Incubeta</t>
+          <t>Gravityer</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>https://incubeta.com</t>
+          <t>https://gravityer.com</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -2158,39 +2158,39 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Altavia WONe</t>
+          <t>Kloc Technologies</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>https://wone.ae</t>
+          <t>https://kloctechnologies.com</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Autumn</t>
+          <t>Chain Reaction</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>https://weareautumn.com</t>
+          <t>https://chainreaction.ae</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -2202,17 +2202,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Emerce Consulting</t>
+          <t>Assembly MENA (Assembly Global)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>https://emerceconsulting.com</t>
+          <t>https://assemblyglobal.com</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Consulting &amp; Strategy Firms</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Mind Digital Group</t>
+          <t>Incubeta</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>https://minddigital.com</t>
+          <t>https://incubeta.com</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -2246,17 +2246,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Magen2</t>
+          <t>Altavia WONe</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>https://magen2.co.uk</t>
+          <t>https://wone.ae</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -2268,39 +2268,39 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Fabrik</t>
+          <t>Autumn</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>https://fabrik.ae</t>
+          <t>https://weareautumn.com</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Optimite</t>
+          <t>Emerce Consulting</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>https://optimite.ai</t>
+          <t>https://emerceconsulting.com</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Consulting &amp; Strategy Firms</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -2312,34 +2312,34 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Publicis Sapient</t>
+          <t>Mind Digital Group</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>https://publicissapient.com</t>
+          <t>https://minddigital.com</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>eCommerce Today</t>
+          <t>Magen2</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>https://ecommerce-today.com</t>
+          <t>https://magen2.co.uk</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -2349,46 +2349,46 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>TechDivision</t>
+          <t>Fabrik</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>https://techdivision.com</t>
+          <t>https://fabrik.ae</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Persona AI</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>The Epixels</t>
+          <t>Optimite</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>https://epixels.ae</t>
+          <t>https://optimite.ai</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -2400,34 +2400,34 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>NULogic</t>
+          <t>Publicis Sapient</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>https://nulogic.io</t>
+          <t>https://publicissapient.com</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Magebit</t>
+          <t>eCommerce Today</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>https://magebit.com</t>
+          <t>https://ecommerce-today.com</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>EI-Technologies MENA</t>
+          <t>TechDivision</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>https://eit-mena.com</t>
+          <t>https://techdivision.com</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -2466,17 +2466,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>VML (VML Commerce MENA)</t>
+          <t>The Epixels</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>https://vml.com</t>
+          <t>https://epixels.ae</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -2488,17 +2488,17 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Merkle MENA</t>
+          <t>NULogic</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>https://merkle.com</t>
+          <t>https://nulogic.io</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -2510,34 +2510,34 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>GOSH Digital</t>
+          <t>Magebit</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>https://goshdigital.co</t>
+          <t>https://magebit.com</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Folio3 eCommerce</t>
+          <t>EI-Technologies MENA</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>https://folio3.com</t>
+          <t>https://eit-mena.com</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -2554,105 +2554,105 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Elsner Technologies</t>
+          <t>VML (VML Commerce MENA)</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>https://elsner.com</t>
+          <t>https://vml.com</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Aureate Labs</t>
+          <t>Merkle MENA</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>https://aureatelabs.com</t>
+          <t>https://merkle.com</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>The Taco People</t>
+          <t>GOSH Digital</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>https://thetacopeople.com</t>
+          <t>https://goshdigital.co</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Team Rhino</t>
+          <t>Folio3 eCommerce</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>https://teamrhino.ae</t>
+          <t>https://folio3.com</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Brand Hawkers</t>
+          <t>Elsner Technologies</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>https://brandhawkers.com</t>
+          <t>https://elsner.com</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -2664,12 +2664,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Globosoft</t>
+          <t>Aureate Labs</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>https://globosoft.ae</t>
+          <t>https://aureatelabs.com</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -2679,19 +2679,19 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Vexa</t>
+          <t>The Taco People</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>https://vexa.ae</t>
+          <t>https://thetacopeople.com</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Persona AI</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>B2 Agency</t>
+          <t>Team Rhino</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>https://b2agency.com</t>
+          <t>https://teamrhino.ae</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -2723,19 +2723,19 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Blink Digital</t>
+          <t>Brand Hawkers</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>https://blinkdigital.in</t>
+          <t>https://brandhawkers.com</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -2752,39 +2752,39 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Redseer Strategy Consultants</t>
+          <t>Globosoft</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>https://redseer.com</t>
+          <t>https://globosoft.ae</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Consulting &amp; Strategy Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Deloitte Digital Middle East</t>
+          <t>Vexa</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>https://deloitte.com</t>
+          <t>https://vexa.ae</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -2796,17 +2796,17 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Frenco</t>
+          <t>B2 Agency</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>https://frenco.ae</t>
+          <t>https://b2agency.com</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -2818,61 +2818,61 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Intwo</t>
+          <t>Blink Digital</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>https://intwo.cloud</t>
+          <t>https://blinkdigital.in</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Home of Performance</t>
+          <t>Redseer Strategy Consultants</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>https://hop.rocks</t>
+          <t>https://redseer.com</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Ecommerce Consulting &amp; Strategy Firms</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Novasoft</t>
+          <t>Deloitte Digital Middle East</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>https://novasoft.global</t>
+          <t>https://deloitte.com</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -2884,39 +2884,39 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Valoriz Digital</t>
+          <t>Frenco</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>https://valoriz.com</t>
+          <t>https://frenco.ae</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>ASTUDIO</t>
+          <t>Intwo</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>https://astudio.ae</t>
+          <t>https://intwo.cloud</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -2928,12 +2928,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>SellThru</t>
+          <t>Home of Performance</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>https://sellthruagency.com</t>
+          <t>https://hop.rocks</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -2950,17 +2950,17 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>HAUS 808</t>
+          <t>Novasoft</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>https://haus808.com</t>
+          <t>https://novasoft.global</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -2972,17 +2972,17 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Pixishoot Studio</t>
+          <t>Valoriz Digital</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>https://pixishoot.studio</t>
+          <t>https://valoriz.com</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -2994,17 +2994,17 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Shapes Defined</t>
+          <t>ASTUDIO</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>https://shapesdefined.com</t>
+          <t>https://astudio.ae</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -3016,17 +3016,17 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>PS Agency</t>
+          <t>SellThru</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>https://ps-agency.ai</t>
+          <t>https://sellthruagency.com</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>SL Media</t>
+          <t>HAUS 808</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>https://slmedia.ae</t>
+          <t>https://haus808.com</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -3060,17 +3060,17 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>RND E-Commerce</t>
+          <t>Pixishoot Studio</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>https://rndecommerce.ae</t>
+          <t>https://pixishoot.studio</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -3082,17 +3082,17 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Aegeantic</t>
+          <t>Shapes Defined</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>https://aegeantic.com</t>
+          <t>https://shapesdefined.com</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -3104,17 +3104,17 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Flow71</t>
+          <t>PS Agency</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>https://flow71.com</t>
+          <t>https://ps-agency.ai</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -3126,122 +3126,122 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>SEO Sherpa</t>
+          <t>SL Media</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>https://seosherpa.com</t>
+          <t>https://slmedia.ae</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Calliweb</t>
+          <t>RND E-Commerce</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>https://calliweb.fr</t>
+          <t>https://rndecommerce.ae</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Tarjama</t>
+          <t>Aegeantic</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>https://tarjama.com</t>
+          <t>https://aegeantic.com</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Uplo</t>
+          <t>Flow71</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>https://uplo.io</t>
+          <t>https://flow71.com</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>NIMA Digital</t>
+          <t>SEO Sherpa</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>https://nimadigital.ae</t>
+          <t>https://seosherpa.com</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Consulting Firms</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>KPI</t>
+          <t>Calliweb</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>https://kpi.co</t>
+          <t>https://calliweb.fr</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -3251,85 +3251,85 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>e-CENS</t>
+          <t>Tarjama</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>https://e-cens.com</t>
+          <t>https://tarjama.com</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Ungrammary</t>
+          <t>Uplo</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>https://ungrammary.com</t>
+          <t>https://uplo.io</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Prism Digital</t>
+          <t>NIMA Digital</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>https://prism-me.com</t>
+          <t>https://nimadigital.ae</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Fashion Ecommerce Consulting Firms</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Persona AI</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Aarialife Technologies</t>
+          <t>KPI</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>https://aarialife.com</t>
+          <t>https://kpi.co</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -3339,24 +3339,24 @@
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Cartello</t>
+          <t>e-CENS</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>https://cartello.io</t>
+          <t>https://e-cens.com</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
@@ -3368,17 +3368,17 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Acquisit</t>
+          <t>Ungrammary</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>https://acquisit.io</t>
+          <t>https://ungrammary.com</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
@@ -3390,39 +3390,39 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Wayve Media</t>
+          <t>Prism Digital</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>https://wayvemedia.com</t>
+          <t>https://prism-me.com</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Feed Management Specialists</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Brand Booster</t>
+          <t>Aarialife Technologies</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>https://brandbooster.ae</t>
+          <t>https://aarialife.com</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
@@ -3434,17 +3434,17 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Azkatech</t>
+          <t>Cartello</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>https://azka.tech</t>
+          <t>https://cartello.io</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -3456,17 +3456,17 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Khaleej Digital</t>
+          <t>Acquisit</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>https://khaleejdigital.com</t>
+          <t>https://acquisit.io</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Consulting Firms</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -3478,17 +3478,17 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Steerz</t>
+          <t>Wayve Media</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>https://steerz.net</t>
+          <t>https://wayvemedia.com</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Product Feed Management Specialists</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Brand Booster</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>https://pattern.com</t>
+          <t>https://brandbooster.ae</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -3522,27 +3522,115 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>Azkatech</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>https://azka.tech</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Khaleej Digital</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>https://khaleejdigital.com</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>Fashion Ecommerce Consulting Firms</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Steerz</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>https://steerz.net</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Autommerce OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>https://pattern.com</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Autommerce OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
           <t>NEXA</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>https://digitalnexa.com</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C145" s="2" t="inlineStr">
         <is>
           <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Autommerce OS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D141"/>
+  <autoFilter ref="A1:D145"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/Autommerce_Partners_UAE.xlsx
+++ b/data/excel/Autommerce_Partners_UAE.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$150</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D145"/>
+  <dimension ref="A1:D150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1630,12 +1630,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Codilar Technologies</t>
+          <t>Clicko Digital</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>https://codilar.com</t>
+          <t>https://clickodigital.com</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -1652,39 +1652,39 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Astound Digital (formerly Astound Commerce)</t>
+          <t>Digital Gravity</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>https://astounddigital.com</t>
+          <t>https://digitalgravity.ae</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Emakina MENA (now Empathy Lab by EPAM)</t>
+          <t>Web Katalyst</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>https://empathylab.com</t>
+          <t>https://webkatalyst.com</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -1696,12 +1696,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>scandiweb</t>
+          <t>Suplex</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>https://scandiweb.com</t>
+          <t>https://suplex.design</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -1711,19 +1711,19 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Creative971</t>
+          <t>AMZ Digital Agency</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>https://creative971.com</t>
+          <t>https://amzdigitalagency.com</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -1733,19 +1733,19 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>LUMINA Commerce</t>
+          <t>Codilar Technologies</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>https://luminacommerce.com</t>
+          <t>https://codilar.com</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -1762,17 +1762,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Prototype</t>
+          <t>Astound Digital (formerly Astound Commerce)</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>https://prototype.ae</t>
+          <t>https://astounddigital.com</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GreenHonchos</t>
+          <t>Emakina MENA (now Empathy Lab by EPAM)</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>https://greenhonchos.com</t>
+          <t>https://empathylab.com</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Consulting &amp; Strategy Firms</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -1806,12 +1806,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Shopvert</t>
+          <t>scandiweb</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>https://shopvert.com</t>
+          <t>https://scandiweb.com</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -1821,19 +1821,19 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>The i.o agency</t>
+          <t>Creative971</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>https://theioagency.com</t>
+          <t>https://creative971.com</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -1850,34 +1850,34 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SQLI Middle East</t>
+          <t>LUMINA Commerce</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>https://sqli.com</t>
+          <t>https://luminacommerce.com</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Vaimo</t>
+          <t>Prototype</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>https://vaimo.com</t>
+          <t>https://prototype.ae</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -1887,24 +1887,24 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>20Three Digital</t>
+          <t>GreenHonchos</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>https://20three.digital</t>
+          <t>https://greenhonchos.com</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Consulting &amp; Strategy Firms</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -1916,39 +1916,39 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Microcorem</t>
+          <t>Shopvert</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>https://microcorem.io</t>
+          <t>https://shopvert.com</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Techies Infotech</t>
+          <t>The i.o agency</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>https://iamtechie.com</t>
+          <t>https://theioagency.com</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -1960,17 +1960,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Krish TechnoLabs</t>
+          <t>SQLI Middle East</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>https://krishtechnolabs.com</t>
+          <t>https://sqli.com</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -1982,12 +1982,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Eastside Co</t>
+          <t>Vaimo</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>https://eastsideco.com</t>
+          <t>https://vaimo.com</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -1997,46 +1997,46 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Magneto IT Solutions</t>
+          <t>20Three Digital</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>https://magnetoitsolutions.com</t>
+          <t>https://20three.digital</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Valtech</t>
+          <t>Microcorem</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>https://valtech.com</t>
+          <t>https://microcorem.io</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2048,17 +2048,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>ArabyAds</t>
+          <t>Techies Infotech</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>https://arabyads.com</t>
+          <t>https://iamtechie.com</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -2070,12 +2070,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Commerce9</t>
+          <t>Krish TechnoLabs</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>https://commerce9.io</t>
+          <t>https://krishtechnolabs.com</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -2092,39 +2092,39 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>UN/COMMON</t>
+          <t>Eastside Co</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>https://uncommonagency.co</t>
+          <t>https://eastsideco.com</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Brainvire</t>
+          <t>Magneto IT Solutions</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>https://brainvire.com</t>
+          <t>https://magnetoitsolutions.com</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Gravityer</t>
+          <t>Valtech</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>https://gravityer.com</t>
+          <t>https://valtech.com</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -2158,105 +2158,105 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Kloc Technologies</t>
+          <t>ArabyAds</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>https://kloctechnologies.com</t>
+          <t>https://arabyads.com</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Chain Reaction</t>
+          <t>Commerce9</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>https://chainreaction.ae</t>
+          <t>https://commerce9.io</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Assembly MENA (Assembly Global)</t>
+          <t>UN/COMMON</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>https://assemblyglobal.com</t>
+          <t>https://uncommonagency.co</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Incubeta</t>
+          <t>Brainvire</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>https://incubeta.com</t>
+          <t>https://brainvire.com</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Altavia WONe</t>
+          <t>Gravityer</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>https://wone.ae</t>
+          <t>https://gravityer.com</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -2268,39 +2268,39 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Autumn</t>
+          <t>Kloc Technologies</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>https://weareautumn.com</t>
+          <t>https://kloctechnologies.com</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Emerce Consulting</t>
+          <t>Chain Reaction</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>https://emerceconsulting.com</t>
+          <t>https://chainreaction.ae</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Consulting &amp; Strategy Firms</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -2312,12 +2312,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Mind Digital Group</t>
+          <t>Assembly MENA (Assembly Global)</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>https://minddigital.com</t>
+          <t>https://assemblyglobal.com</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -2334,17 +2334,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Magen2</t>
+          <t>Incubeta</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>https://magen2.co.uk</t>
+          <t>https://incubeta.com</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Fabrik</t>
+          <t>Altavia WONe</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>https://fabrik.ae</t>
+          <t>https://wone.ae</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -2371,24 +2371,24 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Optimite</t>
+          <t>Autumn</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>https://optimite.ai</t>
+          <t>https://weareautumn.com</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -2400,105 +2400,105 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Publicis Sapient</t>
+          <t>Emerce Consulting</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>https://publicissapient.com</t>
+          <t>https://emerceconsulting.com</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Consulting &amp; Strategy Firms</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>eCommerce Today</t>
+          <t>Mind Digital Group</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>https://ecommerce-today.com</t>
+          <t>https://minddigital.com</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>TechDivision</t>
+          <t>Magen2</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>https://techdivision.com</t>
+          <t>https://magen2.co.uk</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>The Epixels</t>
+          <t>Fabrik</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>https://epixels.ae</t>
+          <t>https://fabrik.ae</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Persona AI</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>NULogic</t>
+          <t>Optimite</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>https://nulogic.io</t>
+          <t>https://optimite.ai</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -2510,17 +2510,17 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Magebit</t>
+          <t>Publicis Sapient</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>https://magebit.com</t>
+          <t>https://publicissapient.com</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -2532,17 +2532,17 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>EI-Technologies MENA</t>
+          <t>eCommerce Today</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>https://eit-mena.com</t>
+          <t>https://ecommerce-today.com</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -2554,39 +2554,39 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>VML (VML Commerce MENA)</t>
+          <t>TechDivision</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>https://vml.com</t>
+          <t>https://techdivision.com</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Merkle MENA</t>
+          <t>The Epixels</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>https://merkle.com</t>
+          <t>https://epixels.ae</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -2598,17 +2598,17 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>GOSH Digital</t>
+          <t>NULogic</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>https://goshdigital.co</t>
+          <t>https://nulogic.io</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -2620,17 +2620,17 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Folio3 eCommerce</t>
+          <t>Magebit</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>https://folio3.com</t>
+          <t>https://magebit.com</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce System Integration Companies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -2642,17 +2642,17 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Elsner Technologies</t>
+          <t>EI-Technologies MENA</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>https://elsner.com</t>
+          <t>https://eit-mena.com</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -2664,61 +2664,61 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Aureate Labs</t>
+          <t>VML (VML Commerce MENA)</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>https://aureatelabs.com</t>
+          <t>https://vml.com</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>The Taco People</t>
+          <t>Merkle MENA</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>https://thetacopeople.com</t>
+          <t>https://merkle.com</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Team Rhino</t>
+          <t>GOSH Digital</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>https://teamrhino.ae</t>
+          <t>https://goshdigital.co</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Website Development Agencies</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -2730,17 +2730,17 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Brand Hawkers</t>
+          <t>Folio3 eCommerce</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>https://brandhawkers.com</t>
+          <t>https://folio3.com</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce System Integration Companies</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Globosoft</t>
+          <t>Elsner Technologies</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>https://globosoft.ae</t>
+          <t>https://elsner.com</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -2767,19 +2767,19 @@
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Vexa</t>
+          <t>Aureate Labs</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>https://vexa.ae</t>
+          <t>https://aureatelabs.com</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -2789,19 +2789,19 @@
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>B2 Agency</t>
+          <t>The Taco People</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>https://b2agency.com</t>
+          <t>https://thetacopeople.com</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -2811,46 +2811,46 @@
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Persona AI</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Blink Digital</t>
+          <t>Team Rhino</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>https://blinkdigital.in</t>
+          <t>https://teamrhino.ae</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Redseer Strategy Consultants</t>
+          <t>Brand Hawkers</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>https://redseer.com</t>
+          <t>https://brandhawkers.com</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Consulting &amp; Strategy Firms</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -2862,17 +2862,17 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Deloitte Digital Middle East</t>
+          <t>Globosoft</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>https://deloitte.com</t>
+          <t>https://globosoft.ae</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -2884,105 +2884,105 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Frenco</t>
+          <t>Vexa</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>https://frenco.ae</t>
+          <t>https://vexa.ae</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Intwo</t>
+          <t>B2 Agency</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>https://intwo.cloud</t>
+          <t>https://b2agency.com</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Website Development Agencies</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Home of Performance</t>
+          <t>Blink Digital</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>https://hop.rocks</t>
+          <t>https://blinkdigital.in</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Ecommerce Digital Marketing &amp; Performance Agencies</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Novasoft</t>
+          <t>Redseer Strategy Consultants</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>https://novasoft.global</t>
+          <t>https://redseer.com</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Consulting &amp; Strategy Firms</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Valoriz Digital</t>
+          <t>Deloitte Digital Middle East</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>https://valoriz.com</t>
+          <t>https://deloitte.com</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Technology &amp; Digital Transformation Firms</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -2994,39 +2994,39 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>ASTUDIO</t>
+          <t>Frenco</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>https://astudio.ae</t>
+          <t>https://frenco.ae</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Ecommerce CRO &amp; UX/UI Agencies</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>SellThru</t>
+          <t>Intwo</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>https://sellthruagency.com</t>
+          <t>https://intwo.cloud</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -3038,17 +3038,17 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>HAUS 808</t>
+          <t>Home of Performance</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>https://haus808.com</t>
+          <t>https://hop.rocks</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -3060,17 +3060,17 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Pixishoot Studio</t>
+          <t>Novasoft</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>https://pixishoot.studio</t>
+          <t>https://novasoft.global</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -3082,17 +3082,17 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Shapes Defined</t>
+          <t>Valoriz Digital</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>https://shapesdefined.com</t>
+          <t>https://valoriz.com</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -3104,17 +3104,17 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>PS Agency</t>
+          <t>ASTUDIO</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>https://ps-agency.ai</t>
+          <t>https://astudio.ae</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
@@ -3126,17 +3126,17 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>SL Media</t>
+          <t>SellThru</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>https://slmedia.ae</t>
+          <t>https://sellthruagency.com</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
@@ -3148,17 +3148,17 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>RND E-Commerce</t>
+          <t>HAUS 808</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>https://rndecommerce.ae</t>
+          <t>https://haus808.com</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
@@ -3170,17 +3170,17 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Aegeantic</t>
+          <t>Pixishoot Studio</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>https://aegeantic.com</t>
+          <t>https://pixishoot.studio</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
@@ -3192,17 +3192,17 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Flow71</t>
+          <t>Shapes Defined</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>https://flow71.com</t>
+          <t>https://shapesdefined.com</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
@@ -3214,56 +3214,56 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>SEO Sherpa</t>
+          <t>PS Agency</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>https://seosherpa.com</t>
+          <t>https://ps-agency.ai</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Calliweb</t>
+          <t>SL Media</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>https://calliweb.fr</t>
+          <t>https://slmedia.ae</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce Product Photography &amp; Creative Production Agencies</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Tarjama</t>
+          <t>RND E-Commerce</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>https://tarjama.com</t>
+          <t>https://rndecommerce.ae</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -3273,178 +3273,178 @@
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Uplo</t>
+          <t>Aegeantic</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>https://uplo.io</t>
+          <t>https://aegeantic.com</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>NIMA Digital</t>
+          <t>Flow71</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>https://nimadigital.ae</t>
+          <t>https://flow71.com</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Consulting Firms</t>
+          <t>Ecommerce Automation &amp; Workflow Consulting Firms</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Persona AI</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>KPI</t>
+          <t>SEO Sherpa</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>https://kpi.co</t>
+          <t>https://seosherpa.com</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>e-CENS</t>
+          <t>Calliweb</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>https://e-cens.com</t>
+          <t>https://calliweb.fr</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Ungrammary</t>
+          <t>Tarjama</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>https://ungrammary.com</t>
+          <t>https://tarjama.com</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Prism Digital</t>
+          <t>Uplo</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>https://prism-me.com</t>
+          <t>https://uplo.io</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Aarialife Technologies</t>
+          <t>NIMA Digital</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>https://aarialife.com</t>
+          <t>https://nimadigital.ae</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+          <t>Fashion Ecommerce Consulting Firms</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Persona AI</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Cartello</t>
+          <t>KPI</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>https://cartello.io</t>
+          <t>https://kpi.co</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce SEO Agencies &amp; Consultants</t>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
@@ -3456,17 +3456,17 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Acquisit</t>
+          <t>e-CENS</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>https://acquisit.io</t>
+          <t>https://e-cens.com</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Digital Marketing Agencies</t>
+          <t>Fashion Ecommerce Personalization &amp; Customer Experience Agencies</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
@@ -3478,56 +3478,56 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Wayve Media</t>
+          <t>Ungrammary</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>https://wayvemedia.com</t>
+          <t>https://ungrammary.com</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Feed Management Specialists</t>
+          <t>Fashion Ecommerce CRO &amp; Conversion Optimization Agencies</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Brand Booster</t>
+          <t>Prism Digital</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>https://brandbooster.ae</t>
+          <t>https://prism-me.com</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Azkatech</t>
+          <t>Aarialife Technologies</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>https://azka.tech</t>
+          <t>https://aarialife.com</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -3537,24 +3537,24 @@
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Autommerce OS</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Khaleej Digital</t>
+          <t>Cartello</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>https://khaleejdigital.com</t>
+          <t>https://cartello.io</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>Fashion Ecommerce Consulting Firms</t>
+          <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
@@ -3566,39 +3566,39 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Steerz</t>
+          <t>Acquisit</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>https://steerz.net</t>
+          <t>https://acquisit.io</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Fashion Ecommerce Digital Marketing Agencies</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Autommerce OS</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Pattern</t>
+          <t>Wayve Media</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>https://pattern.com</t>
+          <t>https://wayvemedia.com</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+          <t>Ecommerce Product Feed Management Specialists</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
@@ -3610,27 +3610,137 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>Brand Booster</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>https://brandbooster.ae</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Autommerce OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Azkatech</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>https://azka.tech</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce PIM / ERP / Inventory Management Consultants</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Khaleej Digital</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>https://khaleejdigital.com</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>Fashion Ecommerce Consulting Firms</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Steerz</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>https://steerz.net</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Autommerce OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>https://pattern.com</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>Ecommerce Product Catalog Management &amp; Data Entry Agencies</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Autommerce OS</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
           <t>NEXA</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>https://digitalnexa.com</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>Ecommerce SEO Agencies &amp; Consultants</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Autommerce OS</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D145"/>
+  <autoFilter ref="A1:D150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/excel/Autommerce_Partners_UAE.xlsx
+++ b/data/excel/Autommerce_Partners_UAE.xlsx
@@ -7,10 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Partners" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company details" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decision makers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Partners'!$A$1:$D$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Company details'!$A$1:$G$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Decision makers'!$A$1:$G$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,8 +30,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -60,10 +68,10 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -427,19 +435,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F4E79"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D150"/>
+  <dimension ref="A1:G150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="72" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Company Name</t>
@@ -458,6 +470,21 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Product Fit</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Emails</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -482,6 +509,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -504,6 +534,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -526,6 +559,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -548,6 +584,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -570,6 +609,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -592,6 +634,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -614,6 +659,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E8" s="2" t="inlineStr"/>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -636,6 +684,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -658,6 +709,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -680,6 +734,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -702,6 +759,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E12" s="2" t="inlineStr"/>
+      <c r="F12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -724,6 +784,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E13" s="2" t="inlineStr"/>
+      <c r="F13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -746,6 +809,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E14" s="2" t="inlineStr"/>
+      <c r="F14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -768,6 +834,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E15" s="2" t="inlineStr"/>
+      <c r="F15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -790,6 +859,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E16" s="2" t="inlineStr"/>
+      <c r="F16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -812,6 +884,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E17" s="2" t="inlineStr"/>
+      <c r="F17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -834,6 +909,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E18" s="2" t="inlineStr"/>
+      <c r="F18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -856,6 +934,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E19" s="2" t="inlineStr"/>
+      <c r="F19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -878,6 +959,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E20" s="2" t="inlineStr"/>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -900,6 +984,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -922,6 +1009,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E22" s="2" t="inlineStr"/>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -944,6 +1034,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E23" s="2" t="inlineStr"/>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -966,6 +1059,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -988,6 +1084,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1010,6 +1109,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1032,6 +1134,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1054,6 +1159,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1076,6 +1184,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E29" s="2" t="inlineStr"/>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1098,6 +1209,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E30" s="2" t="inlineStr"/>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1120,6 +1234,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E31" s="2" t="inlineStr"/>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1142,6 +1259,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1164,6 +1284,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1186,6 +1309,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1208,6 +1334,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1230,6 +1359,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1252,6 +1384,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1274,6 +1409,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1296,6 +1434,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -1318,6 +1459,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E40" s="2" t="inlineStr"/>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -1340,6 +1484,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E41" s="2" t="inlineStr"/>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1362,6 +1509,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E42" s="2" t="inlineStr"/>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -1384,6 +1534,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E43" s="2" t="inlineStr"/>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -1406,6 +1559,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E44" s="2" t="inlineStr"/>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1428,6 +1584,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1450,6 +1609,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1472,6 +1634,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1494,6 +1659,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1516,6 +1684,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1538,6 +1709,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -1560,6 +1734,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E51" s="2" t="inlineStr"/>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -1582,6 +1759,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -1604,6 +1784,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E53" s="2" t="inlineStr"/>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -1626,6 +1809,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E54" s="2" t="inlineStr"/>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -1648,6 +1834,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E55" s="2" t="inlineStr"/>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -1670,6 +1859,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -1692,6 +1884,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E57" s="2" t="inlineStr"/>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -1714,6 +1909,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E58" s="2" t="inlineStr"/>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -1736,6 +1934,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1758,6 +1959,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E60" s="2" t="inlineStr"/>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -1780,6 +1984,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -1802,6 +2009,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E62" s="2" t="inlineStr"/>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -1824,6 +2034,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E63" s="2" t="inlineStr"/>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -1846,6 +2059,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E64" s="2" t="inlineStr"/>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -1868,6 +2084,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E65" s="2" t="inlineStr"/>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -1890,6 +2109,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E66" s="2" t="inlineStr"/>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -1912,6 +2134,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -1934,6 +2159,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E68" s="2" t="inlineStr"/>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -1956,6 +2184,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E69" s="2" t="inlineStr"/>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -1978,6 +2209,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E70" s="2" t="inlineStr"/>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -2000,6 +2234,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E71" s="2" t="inlineStr"/>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -2022,6 +2259,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E72" s="2" t="inlineStr"/>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2044,6 +2284,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E73" s="2" t="inlineStr"/>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2066,6 +2309,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E74" s="2" t="inlineStr"/>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2088,6 +2334,9 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E75" s="2" t="inlineStr"/>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2110,6 +2359,9 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E76" s="2" t="inlineStr"/>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2132,6 +2384,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>info@magnetoitsolutions.com; sales@magnetoitsolutions.com</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>+1 416 904 4907; +971 52 218 8687; +966 59 641 0480; +973 3971 1762; +44 7920 047249; +61 452 581 620; +91 81413 01021</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/magneto-it-solutions</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -2154,6 +2421,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E78" s="2" t="inlineStr"/>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/valtech</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -2176,6 +2450,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>info@arabyads.com</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arabyads</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -2198,6 +2483,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>info@commerce9.io</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>+971 58 581 1523; +971 58 586 6990; +1 847 752 6218; +44 7495 189972; +44 7577 649402; +91 999 508 0656</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/commerce9</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -2220,6 +2520,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>info@uncommonagency.co</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>+1 877 556 3009</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/uncommonagencyco</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -2242,6 +2557,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>info@brainvire.com</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>+1 631 897 7276</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/brainvire-infotech-inc</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -2264,6 +2594,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>info@gravityer.com; admin@gravityer.com</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>+91 90390 23871</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gravity-engineering-services-private-limited</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -2286,6 +2631,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>info@kloctechnologies.com</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>+91 80 4908 3119</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kloc-technologies</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -2308,6 +2668,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>letstalk@chainreaction.ae</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 429 7929; +971 2 401 2526; +966 55 070 1627; +962 6 566 2072</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/chain-reaction-digital-services</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -2330,6 +2705,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>newbiz@assemblyglobal.com</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/assemblymena</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -2352,6 +2738,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/incubeta</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -2374,6 +2767,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>aida@wone.ae; aida.sahraoui@altavia-wone.com</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>+971 58 260 2419</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wone-altavia</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -2396,6 +2804,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>partners@weareautumn.com; sales@weareautumn.com</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/autumntechworx</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -2418,6 +2837,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>info@emerceconsulting.com</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>+971 55 311 3948</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/emerce-consulting</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -2440,6 +2874,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>dubai@minddigital.com; hidubai@minddigital.com; hilondon@minddigital.com; hinewyork@minddigital.com</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>+971 58 882 91395; +1 212 796 6904; +1 800 245 2032; +44 20 7849 6867; +44 7402 919 299; +91 11 4100 3450; +91 956 087 5588</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mind-digital-group</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -2462,6 +2911,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E92" s="2" t="inlineStr"/>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>+44 1925 321738</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/magen2</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -2484,6 +2944,17 @@
           <t>Persona AI</t>
         </is>
       </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>hello@fabrik.ae</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fabrik-agency-uae</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -2506,6 +2977,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>contact@optimite.ai</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>+971 56 149 5510</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/optimite</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -2528,6 +3014,13 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/publicissapient</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -2550,6 +3043,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>contact@ecommerce-today.com</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>+1 646 480 0104; +40 738 496 728</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ecommerce-today</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -2572,6 +3080,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>info@techdivision.com</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>+49 8031 2210550</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/techdivision-gmbh</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -2594,6 +3117,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>+971 55 155 7214</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/epixels-shopify-experts-dubai</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -2616,6 +3150,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>sales@nulogic.io</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>+1 469 922 6985; +1 825 805 5341; +52 55 9346 0210; +56 2 2820 4243; +91 44 2254 2000</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nulogic</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -2638,6 +3187,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>info@magebit.com; partners@magebit.com; quote@magebit.com; ae@magebit.com; kw@magebit.com; uk@magebit.com; us@magebit.com</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>+371 2748 2923; +1 217 702 2888; +44 20 4578 7836; +61 3 9028 2084</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/magebit</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -2660,6 +3224,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>contact@eit-mena.com</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 452 0883; +966 11 201 5772</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ei-technologies-mena</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -2682,6 +3261,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vml</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -2704,6 +3290,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>+1 443 542 4000</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/merkle</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -2726,6 +3323,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>mark@goshdigital.co</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr"/>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/goshdigital</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -2748,6 +3356,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E105" s="2" t="inlineStr"/>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>+1 408 412 3813; +1 408 512 1812; +971 4 575 7041; +44 1483 397625; +92 21 3432 3721</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/folio3</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -2770,6 +3389,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>sales@elsner.com</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>+1 607 524 4040; +1 775 501 6655; +91 98 986 07411; +44 7460 069804; +61 468 126 464</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/elsner-technology-pvt--ltd-</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -2792,6 +3426,13 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E107" s="2" t="inlineStr"/>
+      <c r="F107" s="2" t="inlineStr"/>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aureate-labs</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -2814,6 +3455,21 @@
           <t>Persona AI</t>
         </is>
       </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>info@thetacopeople.com; marwan@thetacopeople.com</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>+971 58 507 3121; +971 50 168 8904</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/the-taco-people</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -2836,6 +3492,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>hello@teamrhinoltd.com</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>+971 55 779 6915; +971 58 164 4837</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/trmc-ae</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -2858,6 +3529,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>hello@brandhawkers.com</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>+971 50 993 9255; +91 98100 80875</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/brandhawkers</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -2880,6 +3566,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>info@globosoft.ae</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 874 1144; +971 50 867 7990</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/globosoftofficial</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -2902,6 +3603,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E112" s="2" t="inlineStr"/>
+      <c r="F112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vexa-ae</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -2924,6 +3632,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>hello@b2agency.com; partners@b2agency.com</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>+971 50 136 0122; +44 113 833 0411</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/b2-shopify-agency</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -2946,6 +3669,13 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E114" s="2" t="inlineStr"/>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/blink-digital</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -2968,6 +3698,13 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E115" s="2" t="inlineStr"/>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/redseer</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -2990,6 +3727,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E116" s="2" t="inlineStr"/>
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/deloitte-digital</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3012,6 +3756,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>info@frenco.ae</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr"/>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/croexperts</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -3034,6 +3789,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E118" s="2" t="inlineStr"/>
+      <c r="F118" s="2" t="inlineStr"/>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/intwocloud</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3056,6 +3818,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>info@hop.rocks</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 227 8572; +966 59 779 6587; +94 11 425 8877</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/hopmarketing</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3078,6 +3855,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>contact@novasoft.global; sales@novasoft.sa</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 223 4123; +971 56 712 5155; +966 50 360 2541; +1 713 405 0641</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/novasoftglobal</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -3100,6 +3892,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>info@valoriz.com</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 223 3920; +91 471 270 0666; +91 484 460 6193</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -3122,6 +3925,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E122" s="2" t="inlineStr"/>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>+971 52 221 0876</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/astudioagency</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -3144,6 +3958,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E123" s="2" t="inlineStr"/>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 570 5327</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/sell-thru</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -3166,6 +3991,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>hello@haus808.com</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>+971 58 571 9035</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -3188,6 +4024,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E125" s="2" t="inlineStr"/>
+      <c r="F125" s="2" t="inlineStr"/>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pixishoot</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -3210,6 +4053,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E126" s="2" t="inlineStr"/>
+      <c r="F126" s="2" t="inlineStr"/>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/shapes-defined</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -3232,6 +4082,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>contact@ps-agency.ai</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr"/>
+      <c r="G127" s="2" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -3254,6 +4111,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>hello@slstudio.ae</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>+971 56 839 9199</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -3276,6 +4144,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>hello@rndecommerce.com</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr"/>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/rnd-ecommerce-fulfillment</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -3298,6 +4177,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E130" s="2" t="inlineStr"/>
+      <c r="F130" s="2" t="inlineStr"/>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aegeantic</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -3320,6 +4206,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E131" s="2" t="inlineStr"/>
+      <c r="F131" s="2" t="inlineStr"/>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/flow71</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -3342,6 +4235,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E132" s="2" t="inlineStr"/>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 443 2286; +966 11 207 4497; +1 786 607 1234; +44 20 3519 2102; +65 3125 1133</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/seo-sherpa</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -3364,6 +4268,13 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E133" s="2" t="inlineStr"/>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>+33 1 45 46 91 27</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -3386,6 +4297,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>hello@tarjama.com; info@tarjama.com; sales@tarjama.com</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 561 6821; +966 11 520 2874; +974 6651 4128; +962 79 953 2572; +961 4 715 999; +1 514 917 5271; +33 6 16 59 82 60</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tarjama</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -3408,6 +4334,13 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E135" s="2" t="inlineStr"/>
+      <c r="F135" s="2" t="inlineStr"/>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/uplo-io</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -3430,6 +4363,21 @@
           <t>Persona AI</t>
         </is>
       </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>info@nimadigital.ae</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>+971 55 840 0971</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nima-digital-consulting</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -3452,6 +4400,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>hello@kpi.co; info@kpi.co</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 455 1010</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -3474,6 +4433,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E138" s="2" t="inlineStr"/>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 441 8742; +966 56 500 0079; +1 415 323 0460; +1 833 528 0983</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/e-cens-inc</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -3496,6 +4466,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>coffee@ungrammary.com</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>+91 84338 84571</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/ungrammary-creatives</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -3518,6 +4503,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>info@prism-me.com; sales@prism-me.com</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 332 0808; +1 604 719 1604; +91 882 876 8661</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/prismmarketing</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -3540,6 +4540,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E141" s="2" t="inlineStr"/>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>+971 50 965 2568; +1 647 477 7421; +91 20 2729 3532</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/aarialife</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -3562,6 +4573,13 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E142" s="2" t="inlineStr"/>
+      <c r="F142" s="2" t="inlineStr"/>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cartello-ecommerce</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -3584,6 +4602,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>hello@acquisit.io</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 566 4822</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/acquisit-advertising</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -3606,6 +4639,13 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E144" s="2" t="inlineStr"/>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>+971 56 716 2922</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -3628,6 +4668,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>corporate@brandbooster.ae</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>+971 54 323 5930</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/brand-booster-ae</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -3650,6 +4705,21 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>info@azka.tech</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>+971 50 228 6440; +961 21 429 226; +961 70 504 898</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/azkatech</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -3672,6 +4742,17 @@
           <t>Both</t>
         </is>
       </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>connect@khaleejdigital.com</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>+971 52 495 1632</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -3694,6 +4775,17 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>info@steerz.net</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>+971 50 268 0401</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -3716,6 +4808,21 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>hello@pattern.com</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>+1 888 881 7576</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pattern-hq</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -3738,9 +4845,4562 @@
           <t>Autommerce OS</t>
         </is>
       </c>
+      <c r="E150" s="2" t="inlineStr"/>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>+971 4 432 9464; +971 52 869 2447; +966 9200 31654</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D150"/>
+  <autoFilter ref="A1:G150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F4E79"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G163"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Decision Maker Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Bhargav Thakkar</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bhargav-thakkar</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>COO and Co-Founder</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Magneto IT Solutions</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>https://magnetoitsolutions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Bhavesh Surani</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>CTO and Director</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Magneto IT Solutions</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>https://magnetoitsolutions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Bhavik Shah</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Magneto IT Solutions</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>https://magnetoitsolutions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Bhumi Patel</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="2" t="inlineStr"/>
+      <c r="D5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Magneto IT Solutions</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>https://magnetoitsolutions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Mitul Patel</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="2" t="inlineStr"/>
+      <c r="D6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Magneto IT Solutions</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>https://magnetoitsolutions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Nitesh Behani</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="2" t="inlineStr"/>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/niteshbehani</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>CRO and Co-Founder</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Magneto IT Solutions</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>https://magnetoitsolutions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Pritesh Vegad</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="2" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Magneto IT Solutions</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>https://magnetoitsolutions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Ronak Meghani</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="2" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ronakmeghani</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>CEO and Co-Founder</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Magneto IT Solutions</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>https://magnetoitsolutions.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Adam Cukrowski</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="2" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adamcukrowski</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Regional Managing Director, Valtech MENA</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Valtech</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>https://valtech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Adam Hasemeyer</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr"/>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>CEO, Americas</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Valtech</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>https://valtech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Olivier Padiou</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr"/>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/olivier-padiou-768161</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Global Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Valtech</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>https://valtech.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Imad Sarrouf</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="2" t="inlineStr"/>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/imaddigital</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Chief Growth Officer</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>ArabyAds</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>https://arabyads.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Madhukar Rao</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="2" t="inlineStr"/>
+      <c r="D14" s="2" t="inlineStr"/>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Group CSO</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>ArabyAds</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>https://arabyads.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Mahmoud Fathy</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="2" t="inlineStr"/>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mahmoud-fathy-35153032</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>CEO and Founder</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>ArabyAds</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>https://arabyads.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Mohammad Khartabil</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="2" t="inlineStr"/>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mkhartabil</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>CBDO and Co-Founder</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>ArabyAds</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>https://arabyads.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Tony Bourached</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="2" t="inlineStr"/>
+      <c r="D17" s="2" t="inlineStr"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>CEO, Ritelo</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>ArabyAds</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>https://arabyads.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Anoop Puthukkudy</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="2" t="inlineStr"/>
+      <c r="D18" s="2" t="inlineStr"/>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Commerce9</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>https://commerce9.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Nived Pattan</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nived-pattan-odoo-erp-ecommerce-ai-expert-commerce9</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Commerce9</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>https://commerce9.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Sruthi Nived</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="2" t="inlineStr"/>
+      <c r="D20" s="2" t="inlineStr"/>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Commerce9</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>https://commerce9.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Adam Ali</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adamb12</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Chairperson of the Board</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>UN/COMMON</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>https://uncommonagency.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Brian Gleason</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="2" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr"/>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Director of Lifecycle Marketing</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>UN/COMMON</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>https://uncommonagency.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Micah Levy</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/micah-levy-14516518</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>CEO, North America</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>UN/COMMON</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>https://uncommonagency.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Olivia Gevirtz</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr"/>
+      <c r="D24" s="2" t="inlineStr"/>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Head of Lifecycle Marketing Solutions</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>UN/COMMON</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>https://uncommonagency.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Stephanie Hayward-Johns</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr"/>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Head of Creative Design</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>UN/COMMON</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>https://uncommonagency.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Zaneh Williams</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr"/>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Head of Technology</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>UN/COMMON</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>https://uncommonagency.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Bharat Patel</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bharatwizzy</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, Digital Marketing</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Brainvire</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>https://brainvire.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Chintan Shah</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr"/>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chintan-shah-59176</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer and Founder</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Brainvire</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>https://brainvire.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Hiren Raval</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr"/>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hirentech</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, eCommerce and ERP</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Brainvire</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>https://brainvire.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Maharshi Pancholi</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr"/>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, Mobility Solutions</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Brainvire</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>https://brainvire.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Pragna Vora</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr"/>
+      <c r="D31" s="2" t="inlineStr"/>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Head of Singapore Operations</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Brainvire</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>https://brainvire.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Pratik Roy</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr"/>
+      <c r="D32" s="2" t="inlineStr"/>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Vice President, Microsoft Technologies</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Brainvire</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>https://brainvire.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Kumar Gaurav</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kumar-gaurav-a23a542a3</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Gravityer</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>https://gravityer.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Mounica M</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>mounica.anjali@gmail.com</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mounicam</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Head of Partnerships</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Gravityer</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>https://gravityer.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Abhisarika Das</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>abhisarika.das@kloctechnologies.com</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abhisarikadas</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Founder, CEO and Managing Director</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Kloc Technologies</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>https://kloctechnologies.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Aditya Sethia</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr"/>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Head of Technology and Products</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Kloc Technologies</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>https://kloctechnologies.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Ganesh Prasad</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr"/>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ganesh-prasad-a933195</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Kloc Technologies</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>https://kloctechnologies.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Tina Jain</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr"/>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tina-jain-a9b740272</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Sales and Marketing Head</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Kloc Technologies</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>https://kloctechnologies.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Saif Jarad</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr"/>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/saifjarad</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Chain Reaction</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>https://chainreaction.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Kinloch Magowan</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kinlochmagowan</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner, MENA</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Assembly MENA (Assembly Global)</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>https://assemblyglobal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Ravi Rao</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr"/>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/raviraodxb</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>CEO, MENA</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Assembly MENA (Assembly Global)</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>https://assemblyglobal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Shanil Jagatia</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shaniljagatia</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner, MENA</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Assembly MENA (Assembly Global)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>https://assemblyglobal.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Victoria Webb</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director, Incubeta MENA</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Incubeta</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>https://incubeta.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Aida Sahraoui</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>aida@wone.ae</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aida-wone</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Altavia WONe</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>https://wone.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Nadir Boulila</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Altavia WONe</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>https://wone.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Anand Vardhan</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anand7514</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Autumn</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>https://weareautumn.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Lina Gallagher</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr"/>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/linagallagher</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Managing Director</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Emerce Consulting</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>https://emerceconsulting.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Yusuf Javed</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>yusuf@minddigital.com</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/yusufjaved</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Director</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Mind Digital Group</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>https://minddigital.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Mathew Marchant</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Magen2</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>https://magen2.co.uk</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Bradley Walker</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>brad@fabrik.ae</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Head of Paid Social</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Fabrik</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>https://fabrik.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Dario Neri</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>dario@fabrik.ae</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr"/>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Wholesale Director and Co-Founder</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Fabrik</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>https://fabrik.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Dean Weightman</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>dean@fabrik.ae</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Client Strategy Director</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Fabrik</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>https://fabrik.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Jason West</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>jason@fabrik.ae</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jasonwestt</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director and Founder</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Fabrik</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>https://fabrik.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Anamika Kalwan</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Head of Content and Marketing</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>Optimite</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>https://optimite.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Nancy Verma</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Head of Sales</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>Optimite</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>https://optimite.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Nishant Yadav</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nishant-yadav-ny</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>Optimite</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>https://optimite.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Sushant Yadav</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr"/>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sushantyadav23</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Optimite</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>https://optimite.ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Chady Ghanem</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chadyghanem</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>Publicis Sapient</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>https://publicissapient.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Gökhan Güney</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr"/>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/goguney</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director, Data Strategy and AI, MENA</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>Publicis Sapient</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>https://publicissapient.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Nowfel Zorba</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nowfel-zorba</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>Publicis Sapient</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>https://publicissapient.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Rami Traboulsi</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr"/>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rami-traboulsi-89310a6</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director, Tech and Data Strategy, MENA</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>Publicis Sapient</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>https://publicissapient.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Andreea Bălașa</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr"/>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Chief Clients Officer</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>eCommerce Today</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>https://ecommerce-today.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Diana Matei</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr"/>
+      <c r="D63" s="2" t="inlineStr"/>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Head of Digital Experience</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>eCommerce Today</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>https://ecommerce-today.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Miruna Diaconescu</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr"/>
+      <c r="D64" s="2" t="inlineStr"/>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Director of Operations</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>eCommerce Today</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>https://ecommerce-today.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Olimpia Valentina Chiriacescu</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr"/>
+      <c r="D65" s="2" t="inlineStr"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Chief Client Officer and Co-Founder</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>eCommerce Today</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>https://ecommerce-today.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Paul Adrian Apostu</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr"/>
+      <c r="D66" s="2" t="inlineStr"/>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Chief Growth Officer</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>eCommerce Today</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>https://ecommerce-today.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Stefan Chiriacescu</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr"/>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stefan-chiriacescu</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>eCommerce Today</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>https://ecommerce-today.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Karin Zipperling</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr"/>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Head of Consulting</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>TechDivision</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>https://techdivision.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Kilian Orschau</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr"/>
+      <c r="D69" s="2" t="inlineStr"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>TechDivision</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>https://techdivision.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Stefan Willkommer</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr"/>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>TechDivision</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>https://techdivision.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Thomas Kalteis</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr"/>
+      <c r="D71" s="2" t="inlineStr"/>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Chief Operating Officer</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>TechDivision</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>https://techdivision.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Tim Wagner</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director and CTO</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>TechDivision</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>https://techdivision.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Abhijeet Mishra</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr"/>
+      <c r="D73" s="2" t="inlineStr"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Director of Growth, North America</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>NULogic</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>https://nulogic.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Mani Vadivel</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr"/>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/manivadivel</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>NULogic</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>https://nulogic.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Steve Nicholas</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr"/>
+      <c r="D75" s="2" t="inlineStr"/>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>VP, Business Development</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>NULogic</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>https://nulogic.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Artūrs Krūze</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr"/>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/arturs-kruze</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>CEO and Co-Founder</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Magebit</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>https://magebit.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Kristaps Rjabovs</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr"/>
+      <c r="D77" s="2" t="inlineStr"/>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director and Co-Owner</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>Magebit</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>https://magebit.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Nauris Miķelsons</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr"/>
+      <c r="D78" s="2" t="inlineStr"/>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Head of Development</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>Magebit</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>https://magebit.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Vladislavs Onufrijevs</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr"/>
+      <c r="D79" s="2" t="inlineStr"/>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Head of Project Department</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>Magebit</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>https://magebit.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Bechara Raad</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr"/>
+      <c r="D80" s="2" t="inlineStr"/>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Chairman, NEO-DIS.COM Group</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>EI-Technologies MENA</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>https://eit-mena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Maria Raad</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr"/>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maria-raad-3548b010</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>EI-Technologies MENA</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>https://eit-mena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Samer Dahr</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr"/>
+      <c r="D82" s="2" t="inlineStr"/>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Partner and Director of Sales and Presales</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>EI-Technologies MENA</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>https://eit-mena.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Ahmed Emad</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr"/>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ahmedemad</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Head of Growth</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>VML (VML Commerce MENA)</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>https://vml.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Faysal Abdul Malak</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr"/>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/faysal-abdul-malak-4b595223</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>CEO, UAE</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>VML (VML Commerce MENA)</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>https://vml.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Georges Kallab</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr"/>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/georges-kallab-976a592a</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>New Business and Growth Director</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>VML (VML Commerce MENA)</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>https://vml.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Martin Barta</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr"/>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/martin-barta-mb347</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>MENA Commercial Director</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>VML (VML Commerce MENA)</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>https://vml.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Skopal</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr"/>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreasskopal</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer, MENA</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Merkle MENA</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>https://merkle.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Tarek Daouk</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr"/>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tarekdaouk</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>President, Southern Europe and MENAT</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Merkle MENA</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>https://merkle.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Mark Cijo</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>mark@goshdigital.co</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/markcijo</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>GOSH Digital</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>https://goshdigital.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Adnan Lawai</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr"/>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adnanlawai</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Folio3 eCommerce</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>https://folio3.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Brandon Rimmey</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr"/>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brandon-rimmey</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Director of Ecommerce, Growth and Strategy</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Folio3 eCommerce</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>https://folio3.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Faisal Arshad</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr"/>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/faisal-arshad-majeed</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Vice President</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Folio3 eCommerce</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>https://folio3.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Irfan Khan</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr"/>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mirfankhan</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Director of Salesforce and eCommerce</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Folio3 eCommerce</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>https://folio3.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Rehan Younus</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr"/>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rehanyounus</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Head of Marketing</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Folio3 eCommerce</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>https://folio3.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Harshal Shah</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>harshal@elsner.com</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harshalelsner</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>Elsner Technologies</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>https://elsner.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Karan Chugh</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr"/>
+      <c r="D96" s="2" t="inlineStr"/>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Director, Business and Technology Consulting</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Elsner Technologies</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>https://elsner.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Nikhil Shah</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr"/>
+      <c r="D97" s="2" t="inlineStr"/>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Chief Information Officer</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Elsner Technologies</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>https://elsner.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Raunaq Rayait</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr"/>
+      <c r="D98" s="2" t="inlineStr"/>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Chief Marketing Officer</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Elsner Technologies</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>https://elsner.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Piyush Lathiya</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr"/>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/piyushlathiya</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Aureate Labs</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>https://aureatelabs.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Moinuddin Khan</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/moinuddin-khan-52955547</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and Head of Operations</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>The Taco People</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>https://thetacopeople.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Sana Sajid</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr"/>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sanasajid8910</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>The Taco People</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>https://thetacopeople.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Haris Sami</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>+971 55 779 6915</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr"/>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/harrissami</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Team Rhino</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>https://teamrhino.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Akash Garg</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr"/>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/akashgargbhspl</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and General Manager</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Brand Hawkers</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>https://brandhawkers.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>George Thomas Kochery</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr"/>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/georgekochery</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>Globosoft</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>https://globosoft.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Jobin George</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr"/>
+      <c r="C105" s="2" t="inlineStr"/>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jobin-george-19482a63</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>CEO and Managing Director</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Globosoft</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>https://globosoft.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Mokshit Nahar</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr"/>
+      <c r="C106" s="2" t="inlineStr"/>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mokshit-nahar-1131083a9</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Vexa</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>https://vexa.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Bruce Mead</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr"/>
+      <c r="C107" s="2" t="inlineStr"/>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/brucemead</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Chief Technical Officer</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>B2 Agency</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>https://b2agency.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>James Hyett</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr"/>
+      <c r="C108" s="2" t="inlineStr"/>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jameshyett</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>B2 Agency</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>https://b2agency.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Dooj Ramchandani</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr"/>
+      <c r="C109" s="2" t="inlineStr"/>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/doojramchandani</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>Blink Digital</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>https://blinkdigital.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Rikki Agarwal</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr"/>
+      <c r="C110" s="2" t="inlineStr"/>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rikki-agarwal-79ab6926</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and Chief Business and Operating Officer</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>Blink Digital</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>https://blinkdigital.in</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Aanshul Agarwal</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr"/>
+      <c r="C111" s="2" t="inlineStr"/>
+      <c r="D111" s="2" t="inlineStr"/>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Director, Marketing</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Redseer Strategy Consultants</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>https://redseer.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Anil Kumar</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr"/>
+      <c r="C112" s="2" t="inlineStr"/>
+      <c r="D112" s="2" t="inlineStr"/>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Redseer Strategy Consultants</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>https://redseer.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Jasbir S Juneja</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr"/>
+      <c r="C113" s="2" t="inlineStr"/>
+      <c r="D113" s="2" t="inlineStr"/>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>Redseer Strategy Consultants</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>https://redseer.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Kushal Bhatnagar</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr"/>
+      <c r="C114" s="2" t="inlineStr"/>
+      <c r="D114" s="2" t="inlineStr"/>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>Redseer Strategy Consultants</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>https://redseer.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Mrigank Gutgutia</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr"/>
+      <c r="C115" s="2" t="inlineStr"/>
+      <c r="D115" s="2" t="inlineStr"/>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>Redseer Strategy Consultants</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>https://redseer.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Rohan Agarwal</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr"/>
+      <c r="C116" s="2" t="inlineStr"/>
+      <c r="D116" s="2" t="inlineStr"/>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>Redseer Strategy Consultants</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>https://redseer.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Sandeep Ganediwalla</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr"/>
+      <c r="C117" s="2" t="inlineStr"/>
+      <c r="D117" s="2" t="inlineStr"/>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>Redseer Strategy Consultants</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>https://redseer.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Neil Batson</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr"/>
+      <c r="C118" s="2" t="inlineStr"/>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/neilbatson</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>Deloitte Digital Middle East</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>https://deloitte.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Henry Gordillo</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr"/>
+      <c r="C119" s="2" t="inlineStr"/>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/henrysgordillo</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director, Americas</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>Intwo</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>https://intwo.cloud</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>John von Hofsten</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr"/>
+      <c r="C120" s="2" t="inlineStr"/>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/johnvonhofsten</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Managing Director</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>Home of Performance</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>https://hop.rocks</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Amit Raaj Sobti</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr"/>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>amit.sobti@novasoft.global</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amitsobti</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Director, Sales and Strategy</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>Novasoft</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>https://novasoft.global</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Divesh Sharma</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr"/>
+      <c r="C122" s="2" t="inlineStr"/>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sharmadivesh</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Dynamics 365 Practice Head</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>Novasoft</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>https://novasoft.global</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Vishwanath Ramachandraiah</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr"/>
+      <c r="C123" s="2" t="inlineStr"/>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vishwanathramachandraiah</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Head of Consulting</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>Novasoft</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>https://novasoft.global</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Toufic Araman</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr"/>
+      <c r="C124" s="2" t="inlineStr"/>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/touficaraman</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>ASTUDIO</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>https://astudio.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Ankit Bansal</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr"/>
+      <c r="C125" s="2" t="inlineStr"/>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ankya7</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and General Manager</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>SellThru</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>https://sellthruagency.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Sean Creech</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr"/>
+      <c r="C126" s="2" t="inlineStr"/>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/seancreech</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Business Development Director</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>SellThru</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>https://sellthruagency.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Shaheer Usmani</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr"/>
+      <c r="C127" s="2" t="inlineStr"/>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shaheer-usmani-a03a2040</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and Advisory Board</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>SellThru</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>https://sellthruagency.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Aya Samha</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr"/>
+      <c r="C128" s="2" t="inlineStr"/>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aya-samha-5131a6126</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Managing Director</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Pixishoot Studio</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>https://pixishoot.studio</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Amine Zaanouni</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr"/>
+      <c r="C129" s="2" t="inlineStr"/>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/amine-zaanouni</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Partner, SD Holdings</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Shapes Defined</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>https://shapesdefined.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Walid Shihabi</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr"/>
+      <c r="C130" s="2" t="inlineStr"/>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/walid-shihabi-695198a4</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Board Member</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Shapes Defined</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>https://shapesdefined.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Betül Gümüş</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr"/>
+      <c r="C131" s="2" t="inlineStr"/>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bet%C3%BCl-g%C3%BCm%C3%BC%C5%9F-3b444045</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>RND E-Commerce</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>https://rndecommerce.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Bulent Agalday</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr"/>
+      <c r="C132" s="2" t="inlineStr"/>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bulent-agalday</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>RND E-Commerce</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>https://rndecommerce.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Abdulbaqi Abubakar</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr"/>
+      <c r="C133" s="2" t="inlineStr"/>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abdulbaqiabubakar</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Aegeantic</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>https://aegeantic.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Abdulbasit Abubakar</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr"/>
+      <c r="C134" s="2" t="inlineStr"/>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/abdulbasit-abubakar-34094170</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Co-Managing Director</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Aegeantic</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>https://aegeantic.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Onur Tepeli</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr"/>
+      <c r="C135" s="2" t="inlineStr"/>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/onur-tepeli-27a21021</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Aegeantic</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>https://aegeantic.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Saif Kidwai</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr"/>
+      <c r="C136" s="2" t="inlineStr"/>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/saifkidwai</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Flow71</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>https://flow71.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Andrea Baggio</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr"/>
+      <c r="C137" s="2" t="inlineStr"/>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreabaggio</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Director of Operations</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>SEO Sherpa</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>https://seosherpa.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>James Reynolds</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr"/>
+      <c r="C138" s="2" t="inlineStr"/>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jameshreynolds</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Managing Director</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>SEO Sherpa</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>https://seosherpa.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Nour Al Hassan</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr"/>
+      <c r="C139" s="2" t="inlineStr"/>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nour-al-hassan-106778138</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Tarjama</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>https://tarjama.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Charbel Nasr</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr"/>
+      <c r="C140" s="2" t="inlineStr"/>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/charbel-nasr-4a5bb036</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder, COO and CTO</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Uplo</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>https://uplo.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Nicolas Bruylants</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr"/>
+      <c r="C141" s="2" t="inlineStr"/>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nicolas-bruylants</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and Chief Vision Officer</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Uplo</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>https://uplo.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Marina Di Falco</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr"/>
+      <c r="C142" s="2" t="inlineStr"/>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/marina-di-falco-33212931</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>NIMA Digital</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>https://nimadigital.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Nicola Antonelli</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr"/>
+      <c r="C143" s="2" t="inlineStr"/>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>NIMA Digital</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>https://nimadigital.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Aneesh P</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr"/>
+      <c r="C144" s="2" t="inlineStr"/>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Chief Technology Officer</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>https://kpi.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Mahesh Shetty</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr"/>
+      <c r="C145" s="2" t="inlineStr"/>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner, Audit and Assurance</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>https://kpi.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Mohammed Abdulla Ahli</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr"/>
+      <c r="C146" s="2" t="inlineStr"/>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>https://kpi.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Prabhakar Kamath</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr"/>
+      <c r="C147" s="2" t="inlineStr"/>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Chairman</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>KPI</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>https://kpi.co</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Feras Alhlou</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr"/>
+      <c r="C148" s="2" t="inlineStr"/>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ferasalhlou</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and Chairman</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>e-CENS</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>https://e-cens.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Shereen Aldisi</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr"/>
+      <c r="C149" s="2" t="inlineStr"/>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/shereenaldisi</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Strategy and Growth Director</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>e-CENS</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>https://e-cens.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Rahul KC</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr"/>
+      <c r="C150" s="2" t="inlineStr"/>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/therahulkc</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Ungrammary</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>https://ungrammary.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Swati Verma</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr"/>
+      <c r="C151" s="2" t="inlineStr"/>
+      <c r="D151" s="2" t="inlineStr"/>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Ungrammary</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>https://ungrammary.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Lovetto Nazareth</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr"/>
+      <c r="C152" s="2" t="inlineStr"/>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/lovetto-nazareth-1b39413</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Founder and Creative Director</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Prism Digital</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>https://prism-me.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Chirag Joshi</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr"/>
+      <c r="C153" s="2" t="inlineStr"/>
+      <c r="D153" s="2" t="inlineStr"/>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and President, North America</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Aarialife Technologies</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>https://aarialife.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Vinay Nair</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr"/>
+      <c r="C154" s="2" t="inlineStr"/>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vinayvnair</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and Board Member</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Aarialife Technologies</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>https://aarialife.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Paul Lombard</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr"/>
+      <c r="C155" s="2" t="inlineStr"/>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paullombard00</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Cartello</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>https://cartello.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Ahmed Abubaker</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr"/>
+      <c r="C156" s="2" t="inlineStr"/>
+      <c r="D156" s="2" t="inlineStr"/>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Director of Measurement</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Acquisit</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>https://acquisit.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Edouard Daou</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr"/>
+      <c r="C157" s="2" t="inlineStr"/>
+      <c r="D157" s="2" t="inlineStr"/>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and Managing Partner, KSA</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Acquisit</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>https://acquisit.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>Laurent Rabot</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr"/>
+      <c r="C158" s="2" t="inlineStr"/>
+      <c r="D158" s="2" t="inlineStr"/>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>CRM and Data Visualization Director</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>Acquisit</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>https://acquisit.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Monika Formanowicz</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr"/>
+      <c r="C159" s="2" t="inlineStr"/>
+      <c r="D159" s="2" t="inlineStr"/>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Digital Marketing Director</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Acquisit</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>https://acquisit.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Raya Succar</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr"/>
+      <c r="C160" s="2" t="inlineStr"/>
+      <c r="D160" s="2" t="inlineStr"/>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>Director of Operations and Client Excellence</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>Acquisit</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>https://acquisit.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Timothée Desormeaux</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr"/>
+      <c r="C161" s="2" t="inlineStr"/>
+      <c r="D161" s="2" t="inlineStr"/>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Acquisit</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>https://acquisit.io</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Mohammad Reza ACIM</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr"/>
+      <c r="C162" s="2" t="inlineStr"/>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/e-business</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Brand Booster</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>https://brandbooster.ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>David Wright</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr"/>
+      <c r="C163" s="2" t="inlineStr"/>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-wright-0241b3</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder and CEO</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Pattern</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>https://pattern.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:G163"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>